--- a/交付物/附件1_高风险小区评分全量清单.xlsx
+++ b/交付物/附件1_高风险小区评分全量清单.xlsx
@@ -36006,7 +36006,7 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>上海中誉物业管理有限公司</t>
+          <t>上海中誉城市运营服务有限公司</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
